--- a/Mercury 2.0.xlsx
+++ b/Mercury 2.0.xlsx
@@ -11152,33 +11152,33 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="2" t="str">
+      <c r="A82" s="2">
         <f>Sheet1!A:A</f>
-        <v/>
-      </c>
-      <c r="B82" s="6" t="str">
+        <v>46139</v>
+      </c>
+      <c r="B82" s="5">
         <f>Sheet1!H:H</f>
-        <v/>
+        <v>0.535</v>
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="2" t="str">
+      <c r="A83" s="2">
         <f>Sheet1!A:A</f>
-        <v/>
-      </c>
-      <c r="B83" s="6" t="str">
+        <v>46140</v>
+      </c>
+      <c r="B83" s="5">
         <f>Sheet1!H:H</f>
-        <v/>
+        <v>0.514</v>
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="2" t="str">
+      <c r="A84" s="2">
         <f>Sheet1!A:A</f>
-        <v/>
-      </c>
-      <c r="B84" s="6" t="str">
+        <v>46141</v>
+      </c>
+      <c r="B84" s="5">
         <f>Sheet1!H:H</f>
-        <v/>
+        <v>0.484</v>
       </c>
     </row>
     <row r="85">
@@ -15546,7 +15546,7 @@
         <v>3.44</v>
       </c>
       <c r="H38" s="23">
-        <f t="shared" ref="H38:H81" si="3">+F38-G38</f>
+        <f t="shared" ref="H38:H84" si="3">+F38-G38</f>
         <v>0.587</v>
       </c>
       <c r="I38" s="45">
@@ -17636,55 +17636,148 @@
       </c>
     </row>
     <row r="82" ht="16.5" customHeight="1">
-      <c r="A82" s="51"/>
-      <c r="B82" s="20"/>
-      <c r="C82" s="20"/>
-      <c r="D82" s="20"/>
-      <c r="E82" s="20"/>
-      <c r="F82" s="57"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="59"/>
-      <c r="I82" s="60"/>
-      <c r="J82" s="20"/>
-      <c r="K82" s="61"/>
-      <c r="L82" s="20"/>
-      <c r="M82" s="20"/>
-      <c r="N82" s="58"/>
-      <c r="O82" s="58"/>
+      <c r="A82" s="51">
+        <v>46139.0</v>
+      </c>
+      <c r="B82" s="52">
+        <v>7173.91</v>
+      </c>
+      <c r="C82" s="52">
+        <v>27305.68</v>
+      </c>
+      <c r="D82" s="52">
+        <v>49167.79</v>
+      </c>
+      <c r="E82" s="52">
+        <v>4638.77</v>
+      </c>
+      <c r="F82" s="53">
+        <v>4.336</v>
+      </c>
+      <c r="G82" s="54">
+        <v>3.801</v>
+      </c>
+      <c r="H82" s="23">
+        <f t="shared" si="3"/>
+        <v>0.535</v>
+      </c>
+      <c r="I82" s="55">
+        <v>18.02</v>
+      </c>
+      <c r="J82" s="52">
+        <v>98.56</v>
+      </c>
+      <c r="K82" s="56">
+        <v>0.8532</v>
+      </c>
+      <c r="L82" s="52">
+        <v>96.66</v>
+      </c>
+      <c r="M82" s="52">
+        <v>4706.94</v>
+      </c>
+      <c r="N82" s="54">
+        <v>485.525</v>
+      </c>
+      <c r="O82" s="54">
+        <v>75.945</v>
+      </c>
     </row>
     <row r="83" ht="16.5" customHeight="1">
-      <c r="A83" s="51"/>
-      <c r="B83" s="20"/>
-      <c r="C83" s="20"/>
-      <c r="D83" s="20"/>
-      <c r="E83" s="20"/>
-      <c r="F83" s="57"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="59"/>
-      <c r="I83" s="60"/>
-      <c r="J83" s="20"/>
-      <c r="K83" s="61"/>
-      <c r="L83" s="20"/>
-      <c r="M83" s="20"/>
-      <c r="N83" s="58"/>
-      <c r="O83" s="58"/>
+      <c r="A83" s="51">
+        <v>46140.0</v>
+      </c>
+      <c r="B83" s="52">
+        <v>7138.8</v>
+      </c>
+      <c r="C83" s="52">
+        <v>27029.01</v>
+      </c>
+      <c r="D83" s="52">
+        <v>49141.93</v>
+      </c>
+      <c r="E83" s="52">
+        <v>4614.35</v>
+      </c>
+      <c r="F83" s="53">
+        <v>4.354</v>
+      </c>
+      <c r="G83" s="54">
+        <v>3.84</v>
+      </c>
+      <c r="H83" s="23">
+        <f t="shared" si="3"/>
+        <v>0.514</v>
+      </c>
+      <c r="I83" s="55">
+        <v>17.83</v>
+      </c>
+      <c r="J83" s="52">
+        <v>98.73</v>
+      </c>
+      <c r="K83" s="56">
+        <v>0.8534</v>
+      </c>
+      <c r="L83" s="52">
+        <v>99.43</v>
+      </c>
+      <c r="M83" s="52">
+        <v>4609.79</v>
+      </c>
+      <c r="N83" s="54">
+        <v>486.196</v>
+      </c>
+      <c r="O83" s="54">
+        <v>73.27</v>
+      </c>
     </row>
     <row r="84" ht="16.5" customHeight="1">
-      <c r="A84" s="51"/>
-      <c r="B84" s="20"/>
-      <c r="C84" s="20"/>
-      <c r="D84" s="20"/>
-      <c r="E84" s="20"/>
-      <c r="F84" s="57"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="59"/>
-      <c r="I84" s="60"/>
-      <c r="J84" s="20"/>
-      <c r="K84" s="61"/>
-      <c r="L84" s="20"/>
-      <c r="M84" s="20"/>
-      <c r="N84" s="58"/>
-      <c r="O84" s="58"/>
+      <c r="A84" s="51">
+        <v>46141.0</v>
+      </c>
+      <c r="B84" s="52">
+        <v>7135.95</v>
+      </c>
+      <c r="C84" s="52">
+        <v>27186.99</v>
+      </c>
+      <c r="D84" s="52">
+        <v>48861.81</v>
+      </c>
+      <c r="E84" s="52">
+        <v>4606.78</v>
+      </c>
+      <c r="F84" s="53">
+        <v>4.416</v>
+      </c>
+      <c r="G84" s="54">
+        <v>3.932</v>
+      </c>
+      <c r="H84" s="23">
+        <f t="shared" si="3"/>
+        <v>0.484</v>
+      </c>
+      <c r="I84" s="55">
+        <v>18.81</v>
+      </c>
+      <c r="J84" s="52">
+        <v>98.96</v>
+      </c>
+      <c r="K84" s="56">
+        <v>0.8564</v>
+      </c>
+      <c r="L84" s="52">
+        <v>106.88</v>
+      </c>
+      <c r="M84" s="52">
+        <v>4577.8</v>
+      </c>
+      <c r="N84" s="54">
+        <v>487.119</v>
+      </c>
+      <c r="O84" s="54">
+        <v>72.356</v>
+      </c>
     </row>
     <row r="85" ht="16.5" customHeight="1">
       <c r="A85" s="51"/>

--- a/Mercury 2.0.xlsx
+++ b/Mercury 2.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/7cb8230cb7254a08/Documentos/Python programas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{34351BAB-DD25-412D-B22A-024DB7A2FE6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{41D0D594-9876-4C29-95F7-19FE26FC8955}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="30630" yWindow="1830" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31065" yWindow="2265" windowWidth="21600" windowHeight="11235" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="US10 yt" sheetId="1" r:id="rId1"/>
